--- a/internal_doc/03.开发设计/modulo/testModv0.3.xlsx
+++ b/internal_doc/03.开发设计/modulo/testModv0.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="format well" sheetId="3" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="221">
   <si>
     <t>left</t>
   </si>
@@ -677,6 +677,81 @@
   </si>
   <si>
     <t>综合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'1e+12</t>
+  </si>
+  <si>
+    <t>'1e+28</t>
+  </si>
+  <si>
+    <t>'1.20892581961463e+24</t>
+  </si>
+  <si>
+    <t>'3666890752</t>
+  </si>
+  <si>
+    <t>'1e-60</t>
+  </si>
+  <si>
+    <t>'1e+20</t>
+  </si>
+  <si>
+    <t>'9.41548674588858e-61</t>
+  </si>
+  <si>
+    <t>'123456.789</t>
+  </si>
+  <si>
+    <t>'1000</t>
+  </si>
+  <si>
+    <t>'0.123456791043282</t>
+  </si>
+  <si>
+    <t>'0.123456786735915</t>
+  </si>
+  <si>
+    <t>'123456798.123456789</t>
+  </si>
+  <si>
+    <t>'123456798.123457</t>
+  </si>
+  <si>
+    <t>123465798123456789.123456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.99927105318746e-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000.000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1e+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1e+28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456798.123457</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.123456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456789.123456789</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3378,7 +3453,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -6045,6 +6120,146 @@
       </c>
       <c r="K75" s="2" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" s="1" customFormat="1">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" s="1" customFormat="1">
+      <c r="A77" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" s="1" customFormat="1">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" s="1" customFormat="1">
+      <c r="A79" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/modulo/testModv0.3.xlsx
+++ b/internal_doc/03.开发设计/modulo/testModv0.3.xlsx
@@ -4,20 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="format well" sheetId="3" r:id="rId1"/>
     <sheet name="only problem" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
+    <sheet name="15位1" sheetId="7" r:id="rId5"/>
+    <sheet name="15位2" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="356">
   <si>
     <t>left</t>
   </si>
@@ -504,39 +506,261 @@
     <t>'1.37700048021122e-318</t>
   </si>
   <si>
+    <t>1.7e-308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38254859</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.08885996</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.10147312211088e-41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7734351413857e+39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7e-307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7e-307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7E-307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7e+307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1e-40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7E+308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38254859</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-38254859</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.08885996</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45593810000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.08885996</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-45593810000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000000000000000000000000000000000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114936596</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-114936596</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.74962673</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.74962673</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4559381000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4559381000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-9.22337203685478e+18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l-trunc(l/r)*r</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>l-floor(l/r)*r</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、当left很大，right靠近零时，如1.7e+300 mod 1e-100，会因为除法溢出导致模运算得到inf的结果。2、1.7e+307 mod 1.2345689，1.7e+308 mod 1e+40，发生严重溢出问题，结果偏差极大。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123.456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-9223372036854775807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fmod(l,r)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7e+308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、1.7e+308 mod 1e+40，1.7e+307 mod 1e+40，发生严重溢出问题，结果偏差极大。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、当left很大，right靠近零时，如1.7e+300 mod 1e-100，会因为除法溢出导致模运算得到inf的结果。2、1.7e+307 mod 1.23456789，1.7e+308 mod 1e+40，发生严重溢出问题，结果偏差极大。3、在right&lt;0,且|right|&gt;&gt;&gt;left的情况下，经常出现非常大的偏差，123.456789 mod (-9223372036854775807)，123.456789 mod -1.7e+308。4、在left/right的结果的绝对值在[0,1]之间时，而|right-left|越大，偏差越大。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待选方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'1e+12</t>
+  </si>
+  <si>
+    <t>'1e+28</t>
+  </si>
+  <si>
+    <t>'1.20892581961463e+24</t>
+  </si>
+  <si>
+    <t>'3666890752</t>
+  </si>
+  <si>
+    <t>'1e-60</t>
+  </si>
+  <si>
+    <t>'1e+20</t>
+  </si>
+  <si>
+    <t>'9.41548674588858e-61</t>
+  </si>
+  <si>
+    <t>'123456.789</t>
+  </si>
+  <si>
+    <t>'1000</t>
+  </si>
+  <si>
+    <t>'0.123456791043282</t>
+  </si>
+  <si>
+    <t>'0.123456786735915</t>
+  </si>
+  <si>
+    <t>'123456798.123456789</t>
+  </si>
+  <si>
+    <t>'123456798.123457</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.99927105318746e-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000.000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1e+20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1e+28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456798.123457</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.123456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456789.123456789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>mod</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.7e-308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38254859</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.08885996</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.10147312211088e-41</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.7734351413857e+39</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1.7e-307</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1.7e-307</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1.7E-307</t>
+    <t>-2.4948003869184e+291</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'123465798123456789.123456789</t>
+  </si>
+  <si>
+    <t>123465798123456789.123456789</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -544,15 +768,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1e-40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1.7E+308</t>
+    <t>1.20892581961463e+24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.4948003869184e+291</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -560,198 +780,422 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>38254859</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-38254859</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.08885996</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>45593810000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-0.08885996</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-45593810000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000000000000000000000000000000000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000017"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>114936596</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-114936596</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.74962673</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-0.74962673</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4559381000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-4559381000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-9.22337203685478e+18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>l-trunc(l/r)*r</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>l-floor(l/r)*r</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、当left很大，right靠近零时，如1.7e+300 mod 1e-100，会因为除法溢出导致模运算得到inf的结果。2、1.7e+307 mod 1.2345689，1.7e+308 mod 1e+40，发生严重溢出问题，结果偏差极大。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123.456789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-9223372036854775807</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fmod(l,r)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1.7e+308</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、1.7e+308 mod 1e+40，1.7e+307 mod 1e+40，发生严重溢出问题，结果偏差极大。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、当left很大，right靠近零时，如1.7e+300 mod 1e-100，会因为除法溢出导致模运算得到inf的结果。2、1.7e+307 mod 1.23456789，1.7e+308 mod 1e+40，发生严重溢出问题，结果偏差极大。3、在right&lt;0,且|right|&gt;&gt;&gt;left的情况下，经常出现非常大的偏差，123.456789 mod (-9223372036854775807)，123.456789 mod -1.7e+308。4、在left/right的结果的绝对值在[0,1]之间时，而|right-left|越大，偏差越大。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待选方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>综合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>'1e+12</t>
-  </si>
-  <si>
-    <t>'1e+28</t>
-  </si>
-  <si>
-    <t>'1.20892581961463e+24</t>
-  </si>
-  <si>
-    <t>'3666890752</t>
-  </si>
-  <si>
-    <t>'1e-60</t>
-  </si>
-  <si>
-    <t>'1e+20</t>
-  </si>
-  <si>
-    <t>'9.41548674588858e-61</t>
-  </si>
-  <si>
-    <t>'123456.789</t>
-  </si>
-  <si>
-    <t>'1000</t>
-  </si>
-  <si>
-    <t>'0.123456791043282</t>
-  </si>
-  <si>
-    <t>'0.123456786735915</t>
-  </si>
-  <si>
-    <t>'123456798.123456789</t>
-  </si>
-  <si>
-    <t>'123456798.123457</t>
-  </si>
-  <si>
-    <t>123465798123456789.123456789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.99927105318746e-10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000.000001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1e+20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1e+28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123456798.123457</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.123456789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123456789.123456789</t>
+    <t xml:space="preserve"> fmod(left right) </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>'1000.000001</t>
+  </si>
+  <si>
+    <t>'9.99927105318746e-10</t>
+  </si>
+  <si>
+    <t>'1.23e+15</t>
+  </si>
+  <si>
+    <t>'123.456789123456789</t>
+  </si>
+  <si>
+    <t>'9963000080700.3</t>
+  </si>
+  <si>
+    <t>'9963000080700</t>
+  </si>
+  <si>
+    <t>'1.22999999999996e+15</t>
+  </si>
+  <si>
+    <t>'37.25</t>
+  </si>
+  <si>
+    <t>'37.1520126748322</t>
+  </si>
+  <si>
+    <t>'123.45678912345678</t>
+  </si>
+  <si>
+    <t>'123.4567891234567</t>
+  </si>
+  <si>
+    <t>'9963000080700.31</t>
+  </si>
+  <si>
+    <t>'38</t>
+  </si>
+  <si>
+    <t>'38.0015091548785</t>
+  </si>
+  <si>
+    <t>'1.23456798123456789</t>
+  </si>
+  <si>
+    <t>'996299935439764</t>
+  </si>
+  <si>
+    <t>'0.25</t>
+  </si>
+  <si>
+    <t>'0.336778650425944</t>
+  </si>
+  <si>
+    <t>'1234567891234567.0</t>
+  </si>
+  <si>
+    <t>'0.128086774909407</t>
+  </si>
+  <si>
+    <t>'1.23456789123457e+15</t>
+  </si>
+  <si>
+    <t>'7.80720726794218</t>
+  </si>
+  <si>
+    <t>'7</t>
+  </si>
+  <si>
+    <t>'8.64197523864197e+15</t>
+  </si>
+  <si>
+    <t>'996552174572599</t>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000000000000000000000000000000000000000000000000000000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.128930037127700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.21859703785400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38.0156370443100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.09189330009066330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1234567891234567.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9638527413214567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>996552174572598.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'123456789.123456</t>
+  </si>
+  <si>
+    <t>'1000.00000099999</t>
+  </si>
+  <si>
+    <t>'0.123456001281738</t>
+  </si>
+  <si>
+    <t>'0.123455996974371</t>
+  </si>
+  <si>
+    <t>'123456.7</t>
+  </si>
+  <si>
+    <t>'1000.00072190052</t>
+  </si>
+  <si>
+    <t>'123456700</t>
+  </si>
+  <si>
+    <t>'89.1234560012817</t>
+  </si>
+  <si>
+    <t>'89.1234560041921</t>
+  </si>
+  <si>
+    <t>'123456798.123456</t>
+  </si>
+  <si>
+    <t>'9.99927105318746e-07</t>
+  </si>
+  <si>
+    <t>'1234657</t>
+  </si>
+  <si>
+    <t>'99.992790000345</t>
+  </si>
+  <si>
+    <t>'99</t>
+  </si>
+  <si>
+    <t>'122231043</t>
+  </si>
+  <si>
+    <t>'1225755.123456</t>
+  </si>
+  <si>
+    <t>'9963000080700.36</t>
+  </si>
+  <si>
+    <t>'45</t>
+  </si>
+  <si>
+    <t>'44.9390637419228</t>
+  </si>
+  <si>
+    <t>'123.456789123</t>
+  </si>
+  <si>
+    <t>'9963000080737.16</t>
+  </si>
+  <si>
+    <t>'9963000080737</t>
+  </si>
+  <si>
+    <t>'1.22999999999998e+15</t>
+  </si>
+  <si>
+    <t>'20.25</t>
+  </si>
+  <si>
+    <t>'20.2866242248955</t>
+  </si>
+  <si>
+    <t>'9963000090663.3</t>
+  </si>
+  <si>
+    <t>'9963000090663</t>
+  </si>
+  <si>
+    <t>'37.1333565482685</t>
+  </si>
+  <si>
+    <t>'996299935439770</t>
+  </si>
+  <si>
+    <t>'0.75</t>
+  </si>
+  <si>
+    <t>'0.672176657323065</t>
+  </si>
+  <si>
+    <t>'1.23456798123</t>
+  </si>
+  <si>
+    <t>'996299935443451</t>
+  </si>
+  <si>
+    <t>'996299935443450</t>
+  </si>
+  <si>
+    <t>'0.719281483268641</t>
+  </si>
+  <si>
+    <t>'1.23456</t>
+  </si>
+  <si>
+    <t>'996306376360809</t>
+  </si>
+  <si>
+    <t>'996306376360808</t>
+  </si>
+  <si>
+    <t>'0.774146105409343</t>
+  </si>
+  <si>
+    <t>'1.23e+13</t>
+  </si>
+  <si>
+    <t>'99630000807.0036</t>
+  </si>
+  <si>
+    <t>'99630000807</t>
+  </si>
+  <si>
+    <t>'12299999999999.6</t>
+  </si>
+  <si>
+    <t>'0.44921875</t>
+  </si>
+  <si>
+    <t>'0.449390637419228</t>
+  </si>
+  <si>
+    <t>'99630000807.3716</t>
+  </si>
+  <si>
+    <t>'12299999999954.1</t>
+  </si>
+  <si>
+    <t>'45.8828125</t>
+  </si>
+  <si>
+    <t>'45.881878217759</t>
+  </si>
+  <si>
+    <t>'99630000906.633</t>
+  </si>
+  <si>
+    <t>'99630000906</t>
+  </si>
+  <si>
+    <t>'12299999999921.9</t>
+  </si>
+  <si>
+    <t>'78.1484375</t>
+  </si>
+  <si>
+    <t>'78.1491106354827</t>
+  </si>
+  <si>
+    <t>'9962999354397.71</t>
+  </si>
+  <si>
+    <t>'9962999354397</t>
+  </si>
+  <si>
+    <t>'12299999999999.1</t>
+  </si>
+  <si>
+    <t>'0.87109375</t>
+  </si>
+  <si>
+    <t>'0.870919353437423</t>
+  </si>
+  <si>
+    <t>'9962999354434.51</t>
+  </si>
+  <si>
+    <t>'9962999354434</t>
+  </si>
+  <si>
+    <t>'12299999999999.4</t>
+  </si>
+  <si>
+    <t>'0.625</t>
+  </si>
+  <si>
+    <t>'0.624476805447686</t>
+  </si>
+  <si>
+    <t>'9963063763608.09</t>
+  </si>
+  <si>
+    <t>'9963063763608</t>
+  </si>
+  <si>
+    <t>'12299999999999.9</t>
+  </si>
+  <si>
+    <t>'0.107421875</t>
+  </si>
+  <si>
+    <t>'0.106506261054093</t>
+  </si>
+  <si>
+    <t>'12.8086774909467</t>
+  </si>
+  <si>
+    <t>'11566232895852</t>
+  </si>
+  <si>
+    <t>'779446016493.6</t>
+  </si>
+  <si>
+    <t>123456789.123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89.123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123465798123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1225746.123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123.456789123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44.989737100800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20.216576349</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.138893</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.23456798123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.69113887754880</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.60867355650</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.87552</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.449897371008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45.881177739</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78.149166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.87110897563968</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.62337072618</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.10752</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12345678912345.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>963852741321</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>779446016493.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +1203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,6 +1285,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -914,7 +1367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -965,6 +1418,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3306,7 +3763,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>94</v>
@@ -3461,7 +3918,7 @@
     <col min="3" max="3" width="29.625" customWidth="1"/>
     <col min="4" max="4" width="28.5" customWidth="1"/>
     <col min="5" max="5" width="28.625" customWidth="1"/>
-    <col min="6" max="6" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="26.5" customWidth="1"/>
     <col min="7" max="7" width="26.75" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="25.875" customWidth="1"/>
@@ -3470,42 +3927,42 @@
     <col min="12" max="12" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="23" customFormat="1">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>155</v>
+      <c r="L1" s="22" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -3825,10 +4282,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>42</v>
@@ -3849,7 +4306,7 @@
         <v>11</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>11</v>
@@ -3954,7 +4411,7 @@
         <v>11</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>11</v>
@@ -4418,7 +4875,7 @@
         <v>86</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4733,10 +5190,10 @@
         <v>103</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -4771,10 +5228,10 @@
         <v>105</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -4809,7 +5266,7 @@
         <v>108</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4844,7 +5301,7 @@
         <v>103</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -4879,7 +5336,7 @@
         <v>105</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -4914,7 +5371,7 @@
         <v>108</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -4949,7 +5406,7 @@
         <v>114</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -4984,7 +5441,7 @@
         <v>115</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -5019,7 +5476,7 @@
         <v>116</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -5054,7 +5511,7 @@
         <v>71</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -5089,7 +5546,7 @@
         <v>71</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -5124,7 +5581,7 @@
         <v>71</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="14" customFormat="1">
@@ -5156,13 +5613,13 @@
         <v>18</v>
       </c>
       <c r="J48" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="8" customFormat="1">
@@ -5194,10 +5651,10 @@
         <v>27</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>86</v>
@@ -5235,7 +5692,7 @@
         <v>126</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -5270,7 +5727,7 @@
         <v>126</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="8" customFormat="1">
@@ -5305,7 +5762,7 @@
         <v>131</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>86</v>
@@ -5343,7 +5800,7 @@
         <v>132</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -5369,16 +5826,16 @@
         <v>37</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>134</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="8" customFormat="1">
@@ -5398,25 +5855,25 @@
         <v>38</v>
       </c>
       <c r="F55" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>166</v>
-      </c>
       <c r="H55" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J55" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="L55" s="12" t="s">
         <v>162</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="L55" s="12" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="8" customFormat="1">
@@ -5436,10 +5893,10 @@
         <v>129</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>86</v>
@@ -5451,10 +5908,10 @@
         <v>123</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -5489,7 +5946,7 @@
         <v>124</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -5524,7 +5981,7 @@
         <v>126</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -5559,7 +6016,7 @@
         <v>126</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -5594,7 +6051,7 @@
         <v>131</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -5629,7 +6086,7 @@
         <v>132</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -5664,7 +6121,7 @@
         <v>134</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -5699,7 +6156,7 @@
         <v>134</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -5734,7 +6191,7 @@
         <v>137</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="16" customFormat="1">
@@ -5759,8 +6216,8 @@
       <c r="G65" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>139</v>
+      <c r="H65" s="20" t="s">
+        <v>220</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>139</v>
@@ -5769,7 +6226,7 @@
         <v>140</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5804,12 +6261,12 @@
         <v>142</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="1" t="s">
-        <v>122</v>
+      <c r="A67" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>109</v>
@@ -5839,7 +6296,7 @@
         <v>137</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5874,7 +6331,7 @@
         <v>140</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5899,8 +6356,8 @@
       <c r="G69" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H69" s="18" t="s">
-        <v>18</v>
+      <c r="H69" s="19" t="s">
+        <v>226</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>18</v>
@@ -5909,7 +6366,7 @@
         <v>142</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5944,7 +6401,7 @@
         <v>148</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -5969,8 +6426,8 @@
       <c r="G71" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>149</v>
+      <c r="H71" s="20" t="s">
+        <v>225</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>149</v>
@@ -5979,7 +6436,7 @@
         <v>150</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6014,7 +6471,7 @@
         <v>151</v>
       </c>
       <c r="K72" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6049,7 +6506,7 @@
         <v>126</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6084,7 +6541,7 @@
         <v>126</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6119,7 +6576,7 @@
         <v>126</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="1" customFormat="1">
@@ -6127,16 +6584,16 @@
         <v>64</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>64</v>
@@ -6144,17 +6601,17 @@
       <c r="G76" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J76" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="K76" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="1" customFormat="1">
@@ -6162,16 +6619,16 @@
         <v>69</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>69</v>
@@ -6186,10 +6643,10 @@
         <v>18</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:11" s="1" customFormat="1">
@@ -6197,16 +6654,16 @@
         <v>84</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>101</v>
@@ -6215,51 +6672,51 @@
         <v>101</v>
       </c>
       <c r="H78" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="K78" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:11" s="1" customFormat="1">
       <c r="A79" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="I79" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J79" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -6282,41 +6739,41 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>197</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="40.5">
       <c r="A2" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="C2" s="22"/>
+        <v>188</v>
+      </c>
+      <c r="C2" s="24"/>
     </row>
     <row r="3" spans="1:3" ht="94.5">
       <c r="A3" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="23"/>
+        <v>194</v>
+      </c>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:3" ht="27">
       <c r="A4" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="24"/>
+        <v>193</v>
+      </c>
+      <c r="C4" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6326,4 +6783,1067 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="31.625" customWidth="1"/>
+    <col min="3" max="3" width="23.625" customWidth="1"/>
+    <col min="4" max="5" width="21.25" customWidth="1"/>
+    <col min="6" max="6" width="28.25" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="32.125" customWidth="1"/>
+    <col min="9" max="9" width="31.875" customWidth="1"/>
+    <col min="10" max="10" width="24.625" customWidth="1"/>
+    <col min="11" max="11" width="24.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="23" customFormat="1">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="20.25" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="5" max="5" width="25.625" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="23.875" customWidth="1"/>
+    <col min="8" max="8" width="26.375" customWidth="1"/>
+    <col min="9" max="9" width="27.875" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="29.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>